--- a/output/pdf_financials_xlsx/BMET.xlsx
+++ b/output/pdf_financials_xlsx/BMET.xlsx
@@ -4565,16 +4565,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.179083</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.179083</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.179083</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.179083</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -5051,19 +5051,19 @@
         <v>-0.040151</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.014476</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.05356</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.059031</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.004664</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.004566</v>
       </c>
     </row>
     <row r="104">
@@ -5744,25 +5744,25 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.93387</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-3.444779</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-4.007393</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.15665</v>
+        <v>-6.227813</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.155387</v>
+        <v>-7.543712</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.164041</v>
+        <v>-4.692602</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>29.920799</v>
+        <v>27.963987</v>
       </c>
     </row>
     <row r="119">
@@ -8770,7 +8770,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12386,7 +12390,11 @@
           <t>RESERVES</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -13078,7 +13086,11 @@
           <t>RESERVES (Note 6)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0.179083</v>
       </c>
@@ -14098,7 +14110,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -14366,7 +14382,11 @@
           <t>Payments for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -15906,7 +15926,11 @@
           <t>Share-based compensation capitalized for exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -17646,7 +17670,11 @@
           <t>Payments for commitment for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BMET.xlsx
+++ b/output/pdf_financials_xlsx/BMET.xlsx
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000156</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.163601</v>
+        <v>-0.163757</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.031073</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.163601</v>
+        <v>-0.163757</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.031073</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-104872.4358974359</v>
+        <v>-104972.4358974359</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.07385799999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.023847</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.053488</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.000993</v>
+        <v>0.488599</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.105869</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.342849</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.212885</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>6.370369</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.007041</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.562355</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.710057</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.883541</v>
       </c>
     </row>
     <row r="35">
@@ -2089,40 +2089,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.07385799999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.023847</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.053488</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.000993</v>
+        <v>0.488599</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.105869</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.342849</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.212885</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>6.370369</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.007041</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.562355</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.710057</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.883541</v>
       </c>
     </row>
     <row r="37">
@@ -2605,40 +2605,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.07385799999999999</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.02468</v>
+        <v>0.000833</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.054096</v>
+        <v>0.000608</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.105869</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.378032</v>
+        <v>0.035183</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.288219</v>
+        <v>0.075334</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.452996</v>
+        <v>0.08262700000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.143228</v>
+        <v>0.136187</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.656761</v>
+        <v>0.094406</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.799799</v>
+        <v>0.089742</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.977849</v>
+        <v>0.094308</v>
       </c>
     </row>
     <row r="49">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -33662,7 +33662,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E361" s="5" t="n">

--- a/output/pdf_financials_xlsx/BMET.xlsx
+++ b/output/pdf_financials_xlsx/BMET.xlsx
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.334725</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -14600,7 +14600,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -17748,7 +17752,11 @@
           <t>Purchase of marketable securities (Note 7)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -20272,7 +20280,11 @@
           <t>Private placement 500,000</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
